--- a/calendrier-contenu-scoremaster-150.xlsx
+++ b/calendrier-contenu-scoremaster-150.xlsx
@@ -68,17 +68,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -120,17 +120,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -172,17 +172,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -224,17 +224,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -276,17 +276,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -328,17 +328,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -380,17 +380,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -432,17 +432,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -484,17 +484,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -536,17 +536,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -588,17 +588,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -640,17 +640,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -692,17 +692,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -744,17 +744,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -796,17 +796,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-30</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -848,17 +848,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-30</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -900,17 +900,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -952,17 +952,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1056,17 +1056,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1108,17 +1108,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-03</t>
+          <t xml:space="preserve">2026-10-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1160,17 +1160,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-03</t>
+          <t xml:space="preserve">2026-10-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1212,17 +1212,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-04</t>
+          <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1264,17 +1264,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-04</t>
+          <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1316,17 +1316,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1368,17 +1368,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1420,17 +1420,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1472,17 +1472,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1524,17 +1524,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1576,17 +1576,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1628,17 +1628,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1680,17 +1680,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1732,17 +1732,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1784,17 +1784,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1836,17 +1836,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-10</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-10</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1940,17 +1940,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-11</t>
+          <t xml:space="preserve">2026-10-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1992,17 +1992,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-11</t>
+          <t xml:space="preserve">2026-10-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2044,17 +2044,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2096,17 +2096,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2148,17 +2148,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2200,17 +2200,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2252,17 +2252,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2304,17 +2304,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2356,17 +2356,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2408,17 +2408,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2460,17 +2460,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2512,17 +2512,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2564,17 +2564,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2616,17 +2616,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2668,17 +2668,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2720,17 +2720,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2772,17 +2772,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2824,17 +2824,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2876,17 +2876,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2928,17 +2928,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2980,17 +2980,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3032,17 +3032,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,17 +3084,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-22</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3136,17 +3136,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-22</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3188,17 +3188,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3240,17 +3240,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3292,17 +3292,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3344,17 +3344,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3396,17 +3396,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3448,17 +3448,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3500,17 +3500,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3552,17 +3552,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3604,17 +3604,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-27</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3656,17 +3656,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-27</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3708,17 +3708,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3760,17 +3760,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3812,17 +3812,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3864,17 +3864,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3916,17 +3916,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3968,17 +3968,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4020,17 +4020,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4072,17 +4072,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4124,17 +4124,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4176,17 +4176,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4228,17 +4228,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4280,17 +4280,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-02</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4332,17 +4332,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4384,17 +4384,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-02</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4436,17 +4436,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4488,17 +4488,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4540,17 +4540,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4592,17 +4592,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4644,17 +4644,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4696,17 +4696,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4748,17 +4748,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4800,17 +4800,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4852,17 +4852,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-08</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4904,17 +4904,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-08</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4956,17 +4956,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-08</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5008,17 +5008,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-08</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5060,17 +5060,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-10</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5112,17 +5112,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-10</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5164,17 +5164,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5216,17 +5216,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5268,17 +5268,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-12</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5320,17 +5320,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-12</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5372,17 +5372,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-12</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5424,17 +5424,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5476,17 +5476,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5528,17 +5528,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5580,17 +5580,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5632,17 +5632,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-15</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5684,17 +5684,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5736,17 +5736,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5788,17 +5788,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5840,17 +5840,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5892,17 +5892,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-18</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5944,17 +5944,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-18</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5996,17 +5996,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-19</t>
+          <t xml:space="preserve">2026-11-18</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6048,17 +6048,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-19</t>
+          <t xml:space="preserve">2026-11-18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6100,17 +6100,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-19</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6152,17 +6152,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-19</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6204,17 +6204,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-21</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6256,17 +6256,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-21</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6308,17 +6308,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2026-11-21</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6360,17 +6360,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-22</t>
+          <t xml:space="preserve">2026-11-21</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6412,17 +6412,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6464,17 +6464,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2026-11-22</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6516,17 +6516,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6568,17 +6568,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6620,17 +6620,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6672,17 +6672,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6724,17 +6724,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-26</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6776,17 +6776,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-26</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6828,17 +6828,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-26</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6880,17 +6880,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-26</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6932,17 +6932,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6984,17 +6984,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7036,17 +7036,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-29</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7088,17 +7088,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-29</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7140,17 +7140,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-29</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7192,17 +7192,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-30</t>
+          <t xml:space="preserve">2026-11-29</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundi</t>
+          <t xml:space="preserve">Dimanche</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7244,17 +7244,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7296,17 +7296,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-01</t>
+          <t xml:space="preserve">2026-11-30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mardi</t>
+          <t xml:space="preserve">Lundi</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7348,17 +7348,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7400,17 +7400,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercredi</t>
+          <t xml:space="preserve">Mardi</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7452,17 +7452,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7504,17 +7504,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeudi</t>
+          <t xml:space="preserve">Mercredi</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7556,17 +7556,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7608,17 +7608,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendredi</t>
+          <t xml:space="preserve">Jeudi</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7660,17 +7660,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7712,17 +7712,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samedi</t>
+          <t xml:space="preserve">Vendredi</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7764,17 +7764,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-06</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7816,17 +7816,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-06</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimanche</t>
+          <t xml:space="preserve">Samedi</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 publications par jour, à 08:15 et 20:15, du jour 3 (23 septembre 2026) au jour 77. Les jours 1 et 2 ont été publiés avec l'ancien format. Les 2 publications d'un même jour appartiennent à 2 familles différentes.</t>
+          <t xml:space="preserve">2 publications par jour, à 08:15 et 20:15, du jour 2 (22 septembre 2026) au jour 76. Le jour 1 a été publié avec l'ancien format. Les 2 publications d'un même jour appartiennent à 2 familles différentes.</t>
         </is>
       </c>
     </row>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jours 3 à 77, 2 créneaux par jour.</t>
+          <t xml:space="preserve">Jours 2 à 76, 2 créneaux par jour.</t>
         </is>
       </c>
     </row>
